--- a/ai/data/history/JavaJobs_14082026.xlsx
+++ b/ai/data/history/JavaJobs_14082026.xlsx
@@ -513,14 +513,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="63" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
@@ -535,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: August 14, 2026 - 12:11 AM | Total Jobs: 5</t>
+          <t>Report Generated: August 14, 2026 - 11:54 PM | Total Jobs: 2</t>
         </is>
       </c>
     </row>
@@ -583,32 +583,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Newrelic</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Sr. Staff SWE, Provisioning Platform</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>San Jose, California, USA</t>
+          <t>Portland, Oregon, USA</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5058382007</t>
+          <t>https://job-boards.greenhouse.io/newrelic/jobs/5390637008</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Principal Software Engineer - Vector Search - Elasticsearch</t>
+          <t>Senior Java Engineer - Distributed Systems, Serverless - Elasticsearch</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -643,112 +643,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs?gh_jid=7843348&amp;gh_jid=7843348</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Blackduck</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>DevOps Engineer 3 (Sr DevSec Engineer)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Burlington, MA</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/blackduck/jobs/5293180008</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Attentive</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Onsite Customer Growth</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/attentive/jobs/4227854009</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Zoox (Amazon) (CA)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Senior/Staff Software Engineer - Ride and Fleet Services</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Foster City, CA</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/zoox/c03ac4b4-ad7b-4407-aaea-66ebc09ca579</t>
+          <t>https://jobs.elastic.co/jobs?gh_jid=7734567&amp;gh_jid=7734567</t>
         </is>
       </c>
     </row>
@@ -756,9 +651,6 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
